--- a/results/phi4_14b/comparison_GoTPlainLLM/GoTPlainLLM_results.xlsx
+++ b/results/phi4_14b/comparison_GoTPlainLLM/GoTPlainLLM_results.xlsx
@@ -723,7 +723,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Adamax Optimizer Implementation in TensorFlow
+The `Adamax` class is a subclass of `optimizer_v2.OptimizerV2`, implementing 
+the Adamax optimization algorithm, an extension of the Adam optimizer that uses 
+the infinity norm for adaptive updates. This optimizer combines features from AdaGrad 
+and Adam to address their individual weaknesses.
+Parameters:
+Functionality:
+The `Adamax` optimizer updates model parameters using past and current gradients 
+to ensure stable convergence. It maintains two slots per variable ('m' for first moment 
+and 'v' for second moment) and applies updates through dense or sparse gradient methods.
+Returns:
+This class provides an optimizer implementation that modifies TensorFlow model 
+variables in-place according to the Adamax optimization rule. It does not return any value but 
+returns grouped operations for updating variables through its methods like `_resource_apply_dense` and 
+`_resource_apply_sparse`.
+Exceptions:
+- Raises `ValueError` if invalid values are provided for learning rate, beta parameters, or epsilon.
+- The implementation assumes TensorFlow is installed; otherwise, a `ModuleNotFoundError` may occur.
+Additional Methods:
+  useful for saving and loading the model state.
+Example Usage:
+    adamax_optimizer = Adamax(learning_rate=0.001)
+    # Use adamax_optimizer in a TensorFlow training loop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -840,7 +862,18 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>AgglomerationTransform Class
+This class is a data transformation tool that extends `TransformerMixin` from the scikit-learn library. It clusters data based on labels and applies pooling operations to these clusters, allowing for flexible transformations.
+Parameters:
+Methods:
+1. transform(X):
+   - Parameters: 
+2. inverse_transform(X=None, *, Xt=None):
+   - Parameters:
+Exceptions:
+- Raises ValueError if input data does not meet requirements (e.g., incompatible sizes between X and labels_).
+- Raises errors for unfitted models or invalid inputs as per scikit-learn's `check_is_fitted` method.
+Note: This class assumes that the model has been fitted before transformations are applied. Ensure compatibility of input dimensions with stored label information to avoid errors.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -1052,7 +1085,13 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Parameters:
+Returns:
+A tensor resulting from average pooling on the input data, with an output shape depending on chosen parameters and typically having one fewer dimension than the input when using 'channels_last'.
+Exceptions:
+Incorrect inputs may raise exceptions at runtime, such as TypeError for non-integer strides or ValueError for invalid padding values (e.g., anything other than 'valid' or 'same').
+Functionality:
+Inherits from Pooling1D to perform average pooling on 1-dimensional data. Utilizes `functools.partial` to define a partial function with backend method for 2D pooling operations, facilitating dimensional reduction and feature extraction in convolutional neural networks.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -1264,7 +1303,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>AveragePooling2D class implements a 2D average pooling operation for input tensors,
+a common procedure in convolutional neural networks to reduce dimensionality and extract features.
+Parameters:
+  It defines the height and width of the region from which the average will be calculated.
+  or 'same' (padding such that output has the same height/width as input).
+  ("NCHW") or "channels_last" ("NHWC"). Defaults to the Keras configuration file setting.
+Functionality:
+This class performs average pooling by taking the mean over each `pool_size` region in the input tensor, reducing
+spatial dimensions while preserving significant features. It inherits from `Pooling2D`, which provides the 
+pooling operation (`nn.avg_pool`) and handles dimensional transformations based on `data_format`.
+Exceptions:
+- Invalid values for `pool_size` (e.g., non-positive integers) will raise errors.
+- A stride value of zero or greater than `pool_size` can lead to incorrect results or runtime errors.
+- The `padding` parameter must be either 'valid' or 'same'; any other value will cause an error.
+- `data_format` must be set to "channels_first" or "channels_last"; unsupported values will trigger exceptions.
+The constructor does not return a value explicitly; instead, it initializes the instance with configured pooling parameters.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -1400,7 +1454,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>AveragePooling3D Class
+The `AveragePooling3D` class is a specialized subclass of `Pooling3D`, designed to perform three-dimensional average pooling on input tensors. It inherits functionality from its parent class while focusing specifically on averaging over spatial dimensions.
+Parameters:
+Functionality:
+This class reduces spatial dimensions through averaging within a specified window size (`pool_size`), using strides defined by `strides`, and optionally applying padding as specified. The result is a reduced dimension representation of input data, maintaining important features while mitigating overfitting in machine learning models.
+Exceptions:
+The class relies on its parent `Pooling3D` to manage exceptions. Common issues may arise from invalid parameter values such as negative pool sizes or unrecognized `padding` and `data_format` strings, which could lead to errors depending on the handling within the deep learning framework used.
+Returns:
+The constructor does not directly return a value but initializes an instance of the `AveragePooling3D` class. The behavior during use will depend on inherited methods from `Pooling3D`.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2393,7 +2455,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>BayesianGaussianMixture Class
+This class implements a Bayesian Gaussian Mixture Model, which extends from sklearn's `BaseMixture`. It utilizes Bayesian inference to model data points as originating from one of several Gaussian distributions, each characterized by specific parameters influenced by prior distributions.
+Parameters:
+Methods:
+Returns:
+- Various methods return updated model states or computed probabilities/log-probabilities. 
+  `_get_parameters` returns a tuple with current parameter values.
+Exceptions:
+- ValueError is raised for invalid input configurations such as inappropriate degrees of freedom prior.
+Functionality:
+- Implements Bayesian Gaussian Mixture Models using probabilistic clustering.
+- Utilizes Expectation-Maximization to optimize model parameters.
+- Handles initialization, parameter checking, and probability estimation within its methods.
+Usage:
+The class can be used for clustering tasks where the data is assumed to come from a mixture of Gaussians with priors defined on their parameters. It is part of sklearn's mixture library and relies on NumPy and SciPy for numerical operations.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2926,7 +3002,18 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Convolutional Layer Class
+This class defines a `Conv` layer that inherits from the Keras `Layer` base class, 
+specifically designed for implementing a 2D Convolutional layer as part of a deep learning model.
+Parameters:
+Returns:
+The `Conv` class initializes a convolutional layer with specified parameters. The main return value is an output tensor resulting from applying the convolution operation on input tensors with learned weights.
+Functionality:
+This class implements a 2D Convolutional layer within the Keras framework, performing operations akin to the 'Conv2D' operator in lower-level frameworks like TensorFlow or Theano. It handles initialization of filters and weights via the `__init__` method, constructs the convolution operation in the `build` method, and executes it in the `call` method.
+Exceptions:
+Raises ValueError for invalid parameters such as negative filter numbers, zero kernel sizes or strides, unsupported padding methods, or incompatible input channel dimensions. The class ensures consistency and validity across various configurations and inputs.
+Other Considerations:
+The layer supports causal padding only for 'Conv1D' and 'SeparableConv1D'. It assumes a 'channels_last' data format by default, which may affect compatibility with other frameworks expecting 'channels_first'.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3142,7 +3229,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Conv1D Layer
+This class, `Conv1D`, extends a base convolution layer `Conv` to implement a one-dimensional convolutional neural network (CNN) layer for deep learning models. It is particularly useful in processing sequential data such as text or time series by applying learnable filters to the input data.
+Parameters:
+The constructor initializes these parameters by calling its parent class's initializer with appropriate arguments for setting up the convolutional layer. Additional keyword arguments (`**kwargs`) are accepted and passed to the base Layer class.
+Functionality:
+This layer performs linear transformations using a set of learnable filters convolved over the input data, capturing local patterns. It processes sequences by learning dependencies through configurable parameters like kernel size, strides, and padding, making it ideal for NLP and time-series analysis tasks. 
+Exceptions:
+Invalid values or types for arguments such as `strides`, `kernel_size`, or unsupported `dilation_rate` can raise errors. Ensure provided inputs adhere to expected formats to avoid exceptions. Unsupported configurations (e.g., specific combinations of stride and dilation rates) may require future code enhancements.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3538,7 +3632,9 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>transposed 1-dimensional convolution operations, enabling upsampling of data.
+Raises `ValueError` if strides are not greater than output_padding during initialization. Additional exceptions may be raised due to invalid parameter values or incorrect usage.
+This class supports operations such as forward propagation, gradient computation, and weight updates based on initialized parameters.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3790,7 +3886,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Conv2D Layer
+This class extends `Conv`, providing a Convolutional layer specifically for 2-dimensional input data, such as images or videos. The `Conv2D` initializer sets up the parameters necessary to define and configure convolution operations within neural networks.
+Parameters:
+Returns:
+    None. The constructor initializes instance attributes based on provided parameters, which are then used by the convolutional layer during operations.
+Exceptions:
+    Raises TypeError if incorrect argument types are supplied.
+    Raises ValueError if required arguments like 'filters' or 'kernel_size' are missing, or if invalid values (e.g., negative numbers) are given for certain parameters. Other exceptions may occur due to incompatibilities with data formats or input shapes, potentially leading to memory issues during training.
+Functionality:
+This class is responsible for setting up a 2D convolutional layer within the Keras framework, allowing users to customize various aspects of the convolution operation such as kernel size, strides, padding, and more. It inherits behavior from the base `Conv` class but specifies configurations pertinent to 2-dimensional data.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -4267,7 +4372,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Conv2DTranspose Class
+This class is a subclass of `Conv2D` from Keras, designed to perform transposed convolutions (also known as fractionally-strided convolutions or deconvolutions). It is primarily used for upsampling inputs while maintaining their content. This operation reconstructs the original pattern from a transformed view, often utilized in tasks like image generation and segmentation.
+Parameters:
+Returns:
+The `__init__()` method initializes the parameters and does not return anything. The `build()` method sets up weight variables but returns nothing. The `call()` method returns the output tensor(s) after applying transposed convolution. The `compute_output_shape()` method calculates the shape of the output based on the input shape.
+Functionality:
+This class performs a 2D transposed convolution, effectively upsampling the input data. It includes checks to ensure that strides are not smaller than kernel size and output padding does not exceed stride values along each dimension. The `build` method initializes weights and biases, while `call` applies the transposed convolution operation.
+Exceptions:
+The code raises `ValueError` if stride is less than or equal to output padding or if input dimensions are undefined. It ensures proper configuration of parameters and input shapes, providing error messages for debugging.
+Additional Methods:</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -4499,7 +4613,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>A class representing a 3-dimensional convolutional layer in a neural network, 
+    inheriting from the base `Conv` class.
+    Parameters:
+    ----------
+        The dimensionality of the output space (i.e., the number of filters in the convolution).
+        Specifies the height, width, and depth of the 3D convolution window.
+        The stride length of the convolution for each dimension.
+        Padding type. 'Valid' means no padding, while 'Same' results in padding such that 
+        input and output have the same height/width/dimension size.
+        Specifies the dilation rate for dilated convolution.
+        Number of groups in the convolution. Relevant when input channels and output 
+        filters are divided into groups.
+        Activation function to use. If None, no activation is applied (linear).
+        Whether the layer uses a bias vector.
+        Initializer for the kernel weights matrix.
+        Initializer for the bias vector.
+        Regularizer function applied to the kernel weights matrix.
+        Regularizer function applied to the bias vector.
+        Regularizer function applied to the output of the layer.
+        Constraint function applied to the kernel weights matrix.
+        Constraint function applied to the bias vector.
+        Additional keyword arguments that can be passed for future extensions.
+    Returns:
+    -------
+    None
+    Exceptions:
+    ----------
+    This class initializes a 3D convolutional layer with specified parameters and 
+    relies on the base `Conv` class to handle tensor ranks beyond two. It configures 
+    dimensions of tensors based on their rank and data format, facilitating seamless 
+    integration into deep learning models for tasks like image recognition or video processing.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -4993,7 +5137,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class `Conv3DTranspose` inherits from `Conv3D` and implements a 3D transposed convolution layer, 
+also known as deconvolution or fractionally-strided convolution, for use in Keras deep learning models. 
+Parameters:
+Returns:
+- A tensor representing the result of applying a 3D transposed convolution on input tensors. 
+The shape depends on the `data_format` ('channels_last' or 'channels_first') and layer parameters.
+Raises:
+Functionality:
+The class initializes with specified parameters, ensuring valid configurations. It builds weights 
+and biases based on the provided specifications and performs a transposed convolution operation 
+during calls. The output shape computation considers padding, strides, and other convolutional parameters.
+This layer can upscale an input volume while minimizing information loss, making it suitable for tasks like image generation.
+Additional Methods:
+Exceptions:
+Handles edge cases by validating input dimensions and parameter configurations, raising appropriate exceptions 
+when encountering invalid setups (e.g., stride vs. output padding issues).</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -5139,7 +5298,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Cropping1D Layer
+This class defines a `Cropping1D` layer in Keras, which is used to crop sections from the beginning and end of each temporal slice (samples) of an input tensor along its time dimension. It inherits from the base `Layer` class.
+Parameters:
+Returns:
+- The layer provides three key methods:
+Functionality:
+- The `Cropping1D` layer is designed for 3D input tensors (batch_size, timesteps, features), cropping them along their temporal dimension as specified by the `cropping` parameter.
+- It ensures that the input shape has three dimensions and computes the resulting tensor's shape accordingly. During the forward pass (`call` method), it slices the tensor based on the cropping parameters.
+Exceptions:
+- This layer does not explicitly handle exceptions but relies on Keras to manage typical errors related to input shapes or data types.
+- Potential issues include input type errors if inputs are not 3D tensors, and configuration errors during serialization/deserialization if non-integer values are used for cropping. These would typically result in `ValueError` or `TypeError`.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -5378,7 +5547,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Cropping2D Layer
+This class is a subclass of the `Layer` in Keras and provides functionality for cropping 
+2D input tensors, which is useful for learning from image patches rather than entire images. 
+It can perform both symmetric and asymmetric cropping along height and width dimensions.
+Parameters:
+      This parameter specifies the crop size. It can be an integer for symmetric cropping in both dimensions,
+      a tuple of two integers for separate cropping values in height and width, or a tuple of two tuples
+      specifying top-bottom and left-right crops.
+      or 'channels_last'. If not provided, defaults to Keras global setting ('image_data_format').
+Returns:
+    This class does not return any value. It modifies the incoming tensor in place by cropping it.
+Functionality:
+    The `Cropping2D` layer accepts an input tensor and crops it based on the specified 
+    `cropping` parameter. It supports both 'channels_first' and 'channels_last' data formats,
+    adjusting its operation accordingly.
+Exceptions:
+    Raises a ValueError if:
+      - The `cropping` parameter is not of type int or tuple.
+      - The `cropping` tuple does not have exactly two elements for non-symmetric cropping.
+      - An invalid `data_format` other than 'channels_first' or 'channels_last' is provided.
+Additional Methods:
+Example Usage:
+    layer = Cropping2D(cropping=((1, 2), (3, 4)), data_format='channels_last')</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -5744,7 +5935,13 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Parameters:
+Returns:
+This class provides several methods including:
+Functionality:
+The `Cropping3D` layer is designed to handle 3-dimensional inputs and allows for custom cropping specifications. It supports different data formats ('channels_first' or 'channels_last') and manages various cropping scenarios through its methods.
+Exceptions:
+This class includes error handling to ensure valid input values, particularly for the `cropping` parameter. It raises ValueError with descriptive messages if invalid values are provided. The `compute_output_shape` method also checks that input shapes have 5 dimensions, raising an exception otherwise. Additional validation is done in `call` and `get_config` methods to maintain robust operation.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -6170,7 +6367,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class implements the DBSCAN clustering algorithm, which is an unsupervised machine learning 
+algorithm that identifies clusters in data by grouping points based on their spatial density.
+Parameters:
+                 neighborhood. This is the radius of the circle around each point where we look for 
+                 points belonging to a cluster.
+                       a core point, including the point itself.
+                              Can be 'euclidean', 'manhattan', etc., or a custom function.
+               Euclidean metric.
+Returns:
+    The `fit` method updates the model with cluster information but returns self for chaining operations.
+    The `fit_predict` method trains the model and returns an array of labels representing clusters.
+Exceptions:
+    - Raises ValueError if input data is inconsistent or invalid metric parameters are provided.
+    - MemoryError may occur with large datasets or high eps/min_samples values.
+    - Errors from joblib when n_jobs &gt; 1, suggesting reducing jobs or setting n_jobs=1.
+    - ValueError for issues with NearestNeighbors initialization due to invalid parameters.
+Functionality:
+    The class provides methods to fit the model (`fit`), predict cluster labels (`fit_predict`),
+    and return additional estimator information (`_more_tags`). It uses density-based spatial 
+    clustering, identifying clusters by computing distances and grouping points based on neighborhood 
+    density.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -6547,7 +6764,18 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>DepthwiseConv2D Class
+This class implements a depth-wise 2D convolutional layer, inheriting from TensorFlow's Conv2D. It performs depth-wise separable convolutions where each input channel is convolved independently with its own set of filters, followed by pointwise convolutions.
+Parameters:
+Returns:
+- The output tensor resulting from applying a depth-wise convolution on the input tensor.
+Exceptions:
+- Raises ValueError if input shape has less than 4 dimensions or if the channel dimension is undefined.
+- Raises AttributeError if superclass methods are missing, though this code does not explicitly raise such errors.
+Functionality:
+- Initializes weights and biases based on input specifications.
+- Applies a depth-wise convolution using defined parameters.
+- Supports configuration retrieval via `get_config()` method for model serialization.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -6878,7 +7106,21 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Embedding Layer Class
+This class defines a custom Keras `Layer` for learning word embeddings, commonly used in natural language processing tasks to represent words as dense vectors of fixed size. It allows similar-meaning words to be represented similarly within a multi-dimensional space.
+Parameters:
+Returns:
+An instance of the `Embedding` class, which can be trained and used for predictions within TensorFlow models. It does not return explicit values but modifies internal layer states during computations.
+Functionality:
+- The layer learns dense vector representations (embeddings) for words in a vocabulary.
+- Utilizes an embedding lookup operation to map integer-coded words to their corresponding vectors.
+- Supports variable-length sequences with optional masking via the `mask_zero` parameter.
+- Raises `ValueError` if `input_dim` or `output_dim` are not positive integers, ensuring valid input dimensions.
+Exceptions:
+- Raises `ValueError` for non-positive `input_dim` or `output_dim`.
+- Ensures compatibility of input shapes with specified `input_length`, raising errors on mismatch.
+Usage:
+Embedding layers are typically used as the initial layer in neural networks for text processing tasks to convert integer-coded words into dense vectors, facilitating downstream learning processes.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -8270,7 +8512,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Flask Class
+This class represents a Flask application and provides functionality to create web applications in Python.
+Parameters:
+Returns:
+A Flask instance configured with the specified parameters. It includes methods for routing, error handling, serving files, managing sessions, etc.
+Methods:
+Exceptions:
+The class handles several exceptions related to HTTP errors, user-generated errors, routing issues, etc., providing mechanisms for debugging and error propagation. Errors are logged, and responses are generated accordingly.
+Functionality:
+Flask provides comprehensive features for web application development, including URL routing, request/response handling, template rendering, session management, and more. It encapsulates these functionalities within methods that can be individually or collectively used to build robust applications.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -8804,7 +9055,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class extends `TransformerMixin` and `BaseEstimator` from scikit-learn to provide a customizable transformation pipeline that applies user-defined functions or function-like objects (e.g., lambda) to input datasets. It can handle both individual and joint feature transformations, offering versatility in data preprocessing tasks such as standardization, normalization, and custom transformations.
+Parameters
+----------
+    A function applied to transform the data. Accepts any number/type of arguments but should return an array-like object with the same shape as input.
+    A function used for inverse transforming the data, operating inversely to `func`.
+    If True, performs additional checks on input data validity (e.g., type checks).
+    If True, enables handling of sparse matrix inputs.
+    Determines whether to verify that inverse transformation returns original data.
+    an array of strings for named features, or a callable generating names based on input.
+    Keyword arguments passed to `func`.
+    Keyword arguments passed to `inverse_func`.
+Returns
+-------
+Methods:
+  Returns the validated or modified input X.
+  Raises a warning if not consistent within tolerance levels, otherwise returns None.
+  feature_names_out (if specified). Returns transformed data as numpy array or pandas DataFrame.
+  original form of data. Returns the inverse-transformed data as numpy array or pandas DataFrame.
+  Returns a numpy array of strings (output feature names).
+  Returns transformed data.
+  requirements and statelessness. Returns a dictionary of tags.
+Exceptions
+----------
+Errors may arise during initialization if `func` or `inverse_func` are not callable. During `fit`
+and `transform`, ValueError is raised when input data is incompatible with functions (e.g., non-numeric
+elements). UserWarning is issued if inverse transformations do not strictly reverse the original 
+transformation and 'check_inverse' is True. In `get_feature_names_out`, a ValueError occurs if output feature names
+do not match expectations.
+Functionality
+-------------
+The class provides a comprehensive framework for applying custom transformations to data, including validation,
+feature name handling, and both forward/inverse transformations. It integrates well within scikit-learn pipelines</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -9382,7 +9664,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GaussianMixture Class
+This class implements a Gaussian Mixture Model (GMM), which is a probabilistic model 
+BaseMixture class and provides methods to initialize, fit, and evaluate the model.
+Parameters:
+  multivariate Gaussian distributions. Options are 'full', 'tied', 'diag', 'spherical'.
+  matrices.
+  lowest Bayesian Information Criterion is retained.
+  weights, and precisions. Options are 'kmeans' or custom initialization using provided arrays.
+  If None, initialized during fit.
+  If None, initialized during fit.
+  Gaussian component. If None, initialized during fit.
+  fitting the next model.
+Returns:
+The class provides methods such as `fit`, `predict`, and `score` for training and evaluating 
+the model. It also includes `bic` and `aic` methods for calculating the Bayesian Information 
+Criterion and Akaike Information Criterion, respectively.
+Methods:
+Exceptions:
+Raises exceptions if covariance_type is invalid, input dimensions are incompatible, or 
+initial values have incorrect shapes. The class handles these through checks and raises 
+informative error messages where applicable.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -9538,7 +9840,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GlobalAveragePooling1D Layer
+This class implements a global average pooling operation for 1-dimensional input data,
+extending the `GlobalPooling1D` base class from Keras.
+Parameters:
+                       or 'channels_first'. The default is 'channels_last', which corresponds to 
+                       an input shape of (batch_size, steps, features) or (steps, batch_size, features). 
+Attributes:
+Methods:
+    call(self, inputs, mask=None):
+        Applies global average pooling to the input data along a specified axis.
+        Parameters:
+                    shape compatible based on `data_format`.
+                             certain elements during pooling. It must have True values where the 
+                             data should not be masked.
+        Returns:
+                    according to `keepdims`.
+    compute_mask(self, inputs, mask=None):
+        No masking is applied or computed by this layer in back-propagation steps.
+        Returns:
+            None
+Functionality:
+The `GlobalAveragePooling1D` class performs an average pooling over the specified axis on 
+the input data. It calculates the mean of all values along one dimension (e.g., time) and
+reduces it to a single value for that dimension, effectively summarizing the information in
+the sequence. If a mask is provided, it applies element-wise multiplication before computing
+the average, allowing certain features to be zeroed out.
+Exceptions:
+Potential exceptions can arise if inputs do not conform to expected shapes/types or if an 
+unsupported `data_format` is specified. Specifically, TensorFlow operations may raise errors 
+such as TypeError for non-numeric data types or dimension mismatches during masking or casting
+operations.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -9661,7 +9993,28 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Perform global average pooling over a 4D input tensor.
+    This method applies global average pooling on an input tensor to reduce spatial dimensions by computing 
+    the mean across specified axes, resulting in a tensor that retains feature map information but with reduced size.
+    Parameters:
+      `(batch_size, channels, rows, cols)` if `data_format='channels_first'`. The input is expected to have floating point values.
+      "channels_last".
+    Returns:
+    - A tensor with reduced spatial dimensions, where the mean is calculated across the height and width for each feature map.
+      The shape of the output depends on `self.keepdims`. If `self.keepdims` is True, the resultant tensor will have 
+      the same rank as input but with reduced dimension sizes. Otherwise, it will remove the pooled axes.
+    Functionality:
+    - This operation reduces overfitting by averaging pixel details and preserving larger patterns across feature maps.
+    - It's commonly used at the end of convolutional networks to prepare for fully connected layers or other tasks like 
+      image classification.
+    Exceptions:
+    - The method relies on Keras backend operations to raise exceptions if inputs do not meet expected dimensions or data types.
+    - Invalid `data_format` will result in an error with a message "Unknown data format".
+    - Inputs must be 4D tensors; handling of non-4D tensors should occur at a higher level.
+    Usage:
+    - Typically used as the final layer in convolutional networks to summarize spatial information into feature maps.
+    Note:
+    - This class is part of Keras and inherits from `GlobalPooling2D`.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -9776,7 +10129,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Perform global average pooling on input tensors in a 3D space.
+Parameters:
+  depend on the context from which this parameter originates.
+  like `keepdims` and `data_format`.
+  [1, 2, 3] (height, width, depth), and for 'channels_first', it's [2, 3, 4] (time, frequency, channels).
+  If True, the output maintains the same number of dimensions as the input, except for the 
+  specified axis which is collapsed.
+  depends on the TensorFlow version in use and provides necessary functionality for executing 
+  operations within TensorFlow.
+  affecting how dimensions are interpreted and reduced.
+Returns:
+- A tensor with reduced dimensionality, obtained by averaging over specified axes. The output 
+  maintains the same type as the input tensor, but collapses three spatial dimensions into one 
+  (or two if `keepdims` is True).
+Exceptions:
+- No explicit exceptions handled within this method. However, potential issues may arise if 
+  input tensors are None or have incompatible dimensions for the specified data format and axes.
+Functionality:
+- This method reduces spatial dimensions of the input tensor by averaging over them, based on 
+  whether the `data_format` is 'channels_last' or 'channels_first'. It ensures that essential 
+  features are retained while reducing dimensionality.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -9911,7 +10284,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Applies a global max pooling operation over the time dimension of the input tensor.
+    Parameters
+    ----------
+        Input tensor with shape `(batch_size, steps, features)` if `data_format='channels_last'` or 
+        `(batch_size, features, steps)` if `data_format='channels_first'`. Should be a three-dimensional 
+        tensor.
+        Determines the ordering of dimensions in the inputs. 'channels_last' corresponds to inputs with
+        shape `(batch_size, steps, features)` while 'channels_first' corresponds to inputs with shape 
+        `(batch_size, features, steps)`.
+        Whether to retain reduced dimensions as 1 (i.e., preserving dimensionality) in the output tensor.
+    Returns
+    -------
+    tensor
+        A tensor with maximum values along the specified axis. The resulting shape is 
+        `(batch_size, features)` if `data_format='channels_last'` or `(batch_size, features, 1)` if 
+        `data_format='channels_first'`.
+    Functionality
+    -------------
+    This method implements a global max pooling operation on input data typically representing time series.
+    It computes the maximum value for each feature map across all steps in every batch element. The axis of 
+    Exceptions
+    ----------
+      'channels_last' nor 'channels_first'.
+    Notes
+    -----
+    This class extends Keras's GlobalPooling1D and is designed for sequence processing tasks. It is typically 
+    used after Convolutional or Recurrent Layers to reduce spatial dimensions down to 1 dimension by computing 
+    maximum values along the specified axis.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -10034,7 +10434,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GlobalMaxPooling2D Layer
+This class extends `GlobalPooling2D` to perform global max pooling on its input data,
+reducing spatial dimensions by extracting maximum values across each feature map.
+Parameters:
+  or (batch_size, channels, height, width) for `data_format='channels_first'`. Expected to be a 4D
+  image data representation.
+Returns:
+A tensor resulting from global max pooling over the spatial dimensions. The shape of the returned
+is 'channels_last' or 'channels_first'. This operation retains maximum values for each feature map,
+resulting in a tensor with reduced spatial dimensions and preserved channel information.
+Functionality:
+The `call()` method overrides its parent class's implementation to apply max pooling globally across
+input tensors. Depending on the data format, it computes the maximum value over either height/width 
+or channels/height/width dimensions using backend functions. This effectively summarizes each feature 
+map into a single maximal value, which is particularly useful in convolutional neural networks (CNNs)
+to reduce spatial information while retaining key features.
+Exceptions:
+The function assumes that inputs are correctly formatted 4D tensors and does not include explicit error
+handling for incorrect input types or dimensions. Potential exceptions may occur at higher levels in the 
+pipeline if incompatible data formats or shapes are passed as `inputs`, leading to errors like ValueError
+or TypeError when backend functions are called.
+In conclusion, this code efficiently reduces spatial information by applying global max pooling,
+facilitating faster computation and often improving performance with minimal loss of accuracy compared 
+to other pooling methods.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -10149,7 +10572,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GlobalMaxPooling3D Class
+This class extends Keras's GlobalPooling3D to perform global max pooling on three-dimensional input data, reducing it to a single value for each feature map by taking the maximum along each spatial dimension (1, 2, and 3). The operation is tailored for inputs shaped as 5D tensors, typically used in convolutional neural networks.
+Parameters:
+Returns:
+A tensor of shape `(batch_size, channels)` or `(batch_size, d1, d2, d3, 1)` if keepdims=True, containing the maximum values across each feature map for every example in the batch. The return type matches that of `inputs`.
+Functionality:
+Performs a downsampling operation by applying global max pooling over spatial dimensions, thus reducing input size while maintaining depth (number of feature maps) intact. It computes statistics across entire tensors to produce condensed representations.
+Exceptions:
+- Raises an error if inputs do not conform to the expected 5D shape as per `data_format`.
+- Assumes data types supporting comparison operations for max pooling; otherwise raises runtime errors.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -10249,7 +10681,28 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GlobalPooling1D Layer Class
+This class defines a custom Keras layer that performs global pooling on temporal data, 
+extending the base `Layer` class in TensorFlow's Keras API. The primary purpose of this 
+layer is to apply a global pooling operation across the time dimension (or sequence length) 
+of an input tensor, effectively reducing its spatial dimensions while retaining important features.
+Parameters:
+  Specifies the data format for input tensors. It can be 'channels_last' (default) or 
+  'channels_first'. In 'channels_last', inputs are expected to have shape (batch_size, steps, features), 
+  whereas in 'channels_first', they should have shape (batch_size, features, steps).
+  Determines whether the output dimensions will retain size one for reduced dimensions. If True, 
+  keeps the dimension of length one; otherwise, reduces directly to a scalar.
+The class provides methods for computing the expected output shape and retrieving layer configuration:
+Returns:
+  This is useful for saving and loading models with Keras' `save_model()` and `load_model()` functions.
+Functionality:
+The GlobalPooling1D class sets up configurations such as `data_format` and `keepdims` in the constructor. 
+It computes the output shape to facilitate tensor allocation during model building, enhancing efficiency.
+However, the actual computation on input samples via global pooling must be implemented by subclasses, 
+hence a NotImplementedError is raised if `call()` is invoked directly.
+Exceptions:
+The class may raise a NotImplementedError if its `call()` method is called without being overridden in a subclass. 
+It's also critical to ensure that inputs conform to expected dimensions (ndim=3) and data formats; otherwise, errors could occur during model compilation.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -10351,7 +10804,28 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GlobalPooling2D Layer
+This class defines a `GlobalPooling2D` layer for Keras, designed to perform global pooling operations on 2D data (images). It serves as a foundational structure that can be extended by subclasses to implement specific pooling logic like average or max pooling. The layer reduces spatial dimensions while maintaining depth/channels, making it suitable for tasks such as image classification and object detection.
+Parameters
+----------
+    Determines the default format of input tensors. If None, defaults to Keras's configuration in ~/.keras/keras.json (default is "channels_last").
+    Whether to retain reduced dimensions as single-dimensional entries. Default is False.
+    Additional keyword arguments for subclass-specific attributes passed to the Layer constructor.
+Returns
+-------
+Functionality
+-------------
+The `GlobalPooling2D` class is designed for use in convolutional neural networks (CNNs) to perform global pooling on 4D tensors. It reduces spatial dimensions without altering depth/channels, providing global feature representations.
+Exceptions
+----------
+- ValueError may occur if the input tensor does not have 4 dimensions.
+- An incorrect 'data_format' value can also raise a ValueError.
+Notes
+-----
+This class is intended for extension by subclasses which will implement the specific pooling logic. Direct instantiation and usage without subclassing to define `call` method will lead to NotImplementedError being raised during execution.
+Example Usage
+-------------
+A typical use-case involves creating a custom layer that inherits from `GlobalPooling2D` and implementing the `call` method with specific pooling operations (e.g., average or max pooling).</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -10451,7 +10925,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GlobalPooling3D Layer
+This class defines a `GlobalPooling3D` layer, inheriting from Keras's base `Layer`, 
+aimed at performing global pooling operations on its input to reduce it to a fixed number of outputs. 
+Parameters:
+  - Can be 'channels_first' or 'channels_last'. If not provided, defaults to the backend's format preference.
+  Defaults to False.
+Returns:
+- compute_output_shape method returns a TensorShape object representing the output shape of this layer given an input shape.
+Functionality:
+The class provides a template for global pooling operations in 3D CNNs, primarily through its methods:
+Exceptions:
+- Calls to `call` without an override will result in NotImplementedError.
+- Invalid values for data_format or keepdims may lead to ValueError during execution.
+This layer is designed for use in 3D CNNs, assuming inputs are 5-dimensional tensors. It provides the structural framework</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -10775,7 +11262,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>GroupTimeSeriesSplit
+This class is designed to generate train/test splits for time series data that are grouped by some identifiers, such as timestamps or categorical variables. It supports both 'rolling' and 'expanding' window types for splitting, ensuring there's no overlap between training and testing sets.
+Parameters:
+Methods:
+  - Parameters: 
+  - Parameters:
+Exceptions:
+Functionality:
+The class provides a mechanism for generating cross-validation splits in time series contexts where groups are consecutive parts of data. It ensures that training and testing sets do not overlap, which is crucial for preventing data leakage in non-stationary and trending time series data.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -11000,7 +11495,13 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>The `Kmeans` class implements the K-Means clustering algorithm using object-oriented programming in Python.
+Parameters:
+Returns:
+Functionality:
+This class implements the K-means clustering algorithm, which partitions data points into clusters based on their distances to centroids. It starts with initial guesses of cluster centers and iteratively assigns samples to the nearest centroid, updating centroids until convergence or reaching a maximum number of iterations. The class extends `_BaseModel`, `_Cluster`, and `_IterativeModel`.
+Exceptions:
+The constructor ensures `k` is a positive integer; otherwise, it raises an exception upon initialization. Additional exceptions may be raised by numpy for invalid input data or numerical issues. It's assumed that inputs are validated elsewhere in the code before calling `_fit`.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -11366,7 +11867,21 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>LabelBinarizer is a class designed for transforming labels in multilabel classification problems into a binary format. It extends Scikit-learn's `TransformerMixin` and `BaseEstimator`, providing basic transformation capabilities.
+Parameters:
+Returns:
+Functionality:
+The class provides a way to convert categorical or discrete data into numerical (binary) format suitable for machine learning algorithms. It supports both multi-label and multiclass problems by applying binarization on each label individually or across all classes.
+Exceptions:
+    Raises ValueError if:
+    - `neg_label` is not strictly less than `pos_label`.
+    - Sparse output is enabled with invalid pos/neg labels.
+    - Input data has zero samples.
+    - Multilabel data is encountered when the object was fitted with non-multilabel input.
+    - Other conditions such as unsupported target data types are met.
+Additional:
+The `_more_tags` method provides metadata indicating that one-dimensional label arrays (e.g., lists, numpy arrays) are expected as input.
+Note: The `auto_wrap_output_keys` parameter is not defined in this class.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -11594,7 +12109,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Parameters:
+- The primary parameter across methods is 'y', representing input or target variable as label or categorical value (e.g., 'dog', 'cat').
+- Additional parameters include 'return_inverse' and 'uniques', used in the context of `fit()` and `transform()` to control additional outputs such as inverse transformation results.
+Returns:
+- The `fit()` method returns self, allowing chaining with other methods like `fit_transform()`.
+- The `fit_transform()` method returns an array of encoded numerical values.
+- The `transform()` method returns an array of transformed labels based on learned mappings.
+- The `inverse_transform()` method returns the original labels from encoded numerical values.
+Functionality:
+- This class provides functionality for fitting a label-to-integer mapping, transforming data points using this mapping, and reversing the transformation if needed. It is particularly useful in preprocessing steps where machine learning algorithms require numerical input.
+Exceptions:
+- The class raises a ValueError during `inverse_transform()` if it encounters previously unseen labels, aiding in catching encoding/decoding errors within data pipelines.
+- It ensures that models are only used after being fitted by checking with `check_is_fitted()` to prevent operations on untrained models.
+Additional Methods:
+- `_more_tags()` provides metadata about the transformer, indicating expected input types as 1D arrays or lists.
+Overall, `LabelEncoder` encapsulates label encoding functionality crucial for converting categorical data into a format suitable for machine learning algorithms.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -11905,7 +12435,36 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>LinearRegression implements various methods for linear regression analysis, including Stochastic Gradient Descent (SGD), Direct method using normal equations, QR decomposition, and Singular Value Decomposition (SVD).
+Parameters:
+        The optimization technique or regression method to use. Options are 'sgd', 'direct', 'svd', and 'qr'. Raises ValueError for unsupported methods.
+        Learning rate for gradient descent methods, controlling the update size of model parameters per iteration.
+        Number of iterations over the entire training dataset during fitting.
+        Size of minibatches for stochastic gradient descent. Must be None if method is not 'sgd'. Raises ValueError otherwise.
+        Seed for random number generation to ensure reproducibility during training.
+        Controls progress printing during fitting. Non-zero values enable progress display.
+Attributes:
+        Bias term of the model after fitting.
+        Weight vector of the model after fitting.
+        Cost computed at each epoch during training when applicable.
+Methods:
+    __init__(self, method='direct', eta=0.01, epochs=50, minibatches=None, random_seed=None, print_progress=0):
+        Initializes the LinearRegression model with specified parameters and checks for valid input combinations.
+    _fit(self, X, y, init_params=True):
+        Fits the linear regression model to the data using the chosen method and updates model parameters. Returns self.
+    _normal_equation(self, X, y):
+        Computes model parameters using the normal equation approach when 'direct' method is selected.
+    _net_input(self, X):
+        Calculates the net input as the weighted sum of inputs plus bias term for prediction purposes.
+    _predict(self, X):
+        Predicts target values for given input data using current model parameters.
+    _sum_squared_error_cost(self, y, y_val):
+        Computes and returns the sum-of-squared-error cost between actual and predicted values.
+Raises:
+    ValueError
+        If an unsupported method is provided or if `minibatches` is not None when method != 'sgd'.
+    ZeroDivisionError
+        Unlikely but possible if input data results in singular matrix during SVD.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -12190,7 +12749,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Logistic Regression Class for Binary Classification
+This class implements a logistic regression model using gradient descent 
+Parameters:
+Functionality:
+- The class inherits from three base classes (_BaseModel, _IterativeModel, and _Classifier) 
+  to support iterative model fitting and classification tasks.
+- Implements a logistic regression algorithm using gradient descent for optimization.
+- Supports L2 regularization if `l2_lambda` is greater than 0.
+- Trains the model through epochs and minibatches, updating weights and biases accordingly.
+- Provides methods for making predictions (`predict`, `predict_proba`) and evaluating model performance.
+Returns:
+- Various methods return self to enable method chaining. For example, `_fit()` returns 
+  the instance itself after fitting. The `predict()` method returns binary class predictions,
+Exceptions:
+- Potential exceptions include mismatches in input dimensions or shapes during operations,
+  and numerical issues (e.g., overflow/underflow) with large inputs to the sigmoid function.
+- The target array y is expected to be binary, containing only 0 and 1 values. Inputs not 
+  adhering to these expectations can lead to runtime errors.
+Overall, this class facilitates fitting a logistic regression model to binary classification data,
+optimizing parameters through gradient descent while offering optional regularization.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -12378,7 +12956,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Base class for defining loss functions in Keras.
+This class represents a loss function used during training and evaluation of machine learning models in Keras. It provides a standard framework to calculate, reduce, and configure losses between true values (`y_true`) and predicted values (`y_pred`).
+Parameters:
+Returns:
+    The following methods are available for interacting with the Loss class:
+Functionality:
+    This class serves as a base for all custom loss functions in Keras. Subclasses must implement the `call(y_true, y_pred)` method to define how losses are calculated between inputs and predictions. The class provides utility methods for serialization/deserialization of its configuration (`get_config` and `from_config`) and defines the main reduction strategy via the `__call__` method.
+Exceptions:</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -12548,7 +13133,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>MaxPooling1D is a subclass of Pooling1D designed to perform max pooling operations on one-dimensional input data in deep learning models using Keras. This operation reduces spatial dimensionality by selecting the maximum value from each window, preserving essential features while downscaling.
+Parameters:
+Functionality:
+MaxPooling1D reduces the spatial dimensionality of its inputs by applying a max-pooling operation along the specified axis. It utilizes backend.pool2d with pool_mode set to 'max', ensuring that maximum values are selected during pooling.
+Exceptions:
+This class can raise exceptions if invalid parameters are provided, such as:
+- Non-positive or non-integer pool_size
+- Invalid strides value
+- Unsupported padding types other than 'valid' and 'same'
+- Incorrect data_format values
+Users should handle these potential errors appropriately to ensure smooth operation. Common runtime issues may also arise from resource limitations or incorrect backend usage.
+Returns:
+An instance of MaxPooling1D which can be used as a layer in a Keras model, applying max pooling to reduce dimensionality and preserve important features in the input data.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -12800,7 +13397,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>MaxPooling2D Class
+This class represents a Max Pooling operation for two-dimensional data (such as images) and is a subclass of the general `Pooling2D` class provided by deep learning libraries.
+Parameters:
+Returns:
+A new instance of MaxPooling2D layer configured with specified parameters. This initialization method does not return any value as it sets up object properties upon instantiation.
+Functionality:
+The MaxPooling2D operation is commonly used in Convolutional Neural Networks (CNNs) to reduce the spatial dimensions of feature maps, thereby reducing computation and controlling overfitting by down-sampling input data via non-overlapping maximum values within specified pooling windows. 
+Exceptions:
+- If `data_format` is not 'channels_first' or 'channels_last', a ValueError will be raised.
+- If `pool_size` or `strides` are not tuples of two positive integers, a TypeError or ValueError may occur due to invalid dimensions or types.
+- Providing an unsupported value for `padding` raises a ValueError.
+Edge Cases:
+Ensure that the provided `pool_size` and `strides`, if specified, match the expected format (tuple of two integers) to avoid exceptions. The function relies on Keras configuration settings when certain parameters are not explicitly defined.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -12936,7 +13545,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class implements a 3D Max Pooling layer that inherits from the `Pooling3D` base class.
+Max pooling is a downsampling technique used in convolutional neural networks (CNNs) to reduce 
+dimensionality and prevent overfitting. It selects the maximum value within each pooling window, 
+providing translation invariance.
+Parameters:
+  (depth, height, width). Default is `(2, 2, 2)`.
+  traversing input data. A stride of 1 results in regular pooling.
+  ensures output dimensions are preserved by adding necessary padding.
+  `(batch, channels, depth, height, width)`.
+Returns:
+This method does not return any value directly. It initializes a `MaxPooling3D` instance that 
+applies max pooling operations on input data and updates its state accordingly.
+Functionality:
+The MaxPooling3D layer applies 3D max pooling over inputs using specified window sizes and strides, 
+reducing spatial dimensions while preserving essential features. This is crucial for CNNs to generate 
+more abstract representations of the input data.
+Exceptions:
+This function may raise exceptions if invalid arguments are provided (e.g., negative pool_size or 
+strides). Errors could also occur due to incompatibility with parent class `Pooling3D` or improper 
+usage post-instantiation. These should be handled by the calling code, as this class does not catch 
+them directly.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -13363,7 +13992,40 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Metric Class for Keras
+This abstract class, `Metric`, is designed to serve as a base class for custom metrics in Keras. It provides an interface for evaluating performance during training and testing by calculating and updating metric values based on provided inputs.
+Parameters:
+- __init__(self, dtype=None, name=None):
+Methods:
+- update_state(self, *args, **kwargs): 
+  Raises NotImplementedError. To be implemented in subclasses to update internal states.
+- result(self):
+  Raises NotImplementedError. To be implemented in subclasses to return the current value of the metric.
+- stateless_update_state(self, metric_variables, *args, **kwargs):
+  Accepts `metric_variables` that correspond one-to-one with this object's variables; raises ValueError if not matched.
+- stateless_result(self, metric_variables):
+  Utilizes a StatelessScope to compute results without maintaining internal state. Raises ValueError for mismatched `metric_variables`.
+- stateless_reset_state():
+  Resets the state using a StatelessScope context manager and returns current values of all variables post-reset.
+- get_config(self):
+  Returns configuration dictionary including name and dtype, suitable for saving/loading model configurations.
+- from_config(cls, config):
+  Class method to instantiate a `Metric` object from its saved configuration.
+- __setattr__(self, name, value):
+  Overrides attribute setting with tracking capability if `_tracker` exists.
+Properties:
+- variables(self): 
+  Returns a list of all associated variables.
+- dtype(self): 
+  Provides the data type in use for this metric.
+Returns:
+The class returns various methods' outcomes related to state and operations. Subclasses are expected to override certain methods like `update_state()` and `result()` to provide specific functionality.
+Exceptions:
+Raises NotImplementedError if essential methods (`update_state`, `result`, `reset_state`) are not implemented by subclasses.
+Raises ValueError when the length of `metric_variables` does not match with the number of metric variables in stateless operations.
+Potential exceptions may also occur due to unsupported initializers or incompatible shapes provided to add_variable/add_weight.
+Functionality:
+The Metric class allows for custom metrics creation, enabling performance measurement via user-defined update and result methods. It tracks associated variables' states during training, supports serialization for saving/loading configurations, and offers stateless operations for distributed training contexts.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -13793,7 +14455,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>MultiLabelBinarizer Class
+The `MultiLabelBinarizer` class is designed to transform between multilabel sets and a multilabel indicator format, inheriting from scikit-learn's `TransformerMixin`, `BaseEstimator`. It optionally includes an unused attribute `auto_wrap_output_keys=None`.
+Parameters:
+Functionality:
+- The class provides methods to fit, transform, and inverse-transform multi-label datasets into binary formats suitable for machine learning algorithms. 
+Returns:
+- Methods like `fit()` return self for chaining operations. Transformation methods return transformed arrays of shape `(n_samples, n_features)`.
+- Provides `_more_tags` method with information on expected data types for transformations.
+Exceptions:
+- Raises ValueError if duplicate classes are provided or if the shape of transformed data does not match the fitted model during inverse transformation.
+- Issues warnings for unrecognized classes encountered during transformation.
+Usage Example:
+    mlb = MultiLabelBinarizer(classes=['Class1', 'Class2', 'Class3'])
+    mlb.fit(y)
+    yt = mlb.transform(y)
+The class is particularly useful for handling multilabel classification problems, supporting both dense and sparse representations.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -14955,7 +15632,16 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>OneHotEncoder Class
+This class provides one-hot encoding for categorical variables, transforming them into a 
+numerical format suitable for machine learning algorithms. It handles various scenarios such as 
+dropping categories, dealing with unknown categories, and managing sparse/dense output formats.
+Parameters:
+Methods:
+Exceptions:
+- Raises ValueError for invalid parameter combinations or when encountering unexpected values in the input data.
+- Raises TypeError if input types do not match expected formats.
+The OneHotEncoder class is designed to facilitate preprocessing of categorical data for machine learning tasks. It offers flexibility through various parameters and handles exceptions where necessary, ensuring robust performance with clear error messages.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -15459,7 +16145,61 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class implements the OPTICS (Ordering Points To Identify the Clustering Structure)
+algorithm, which extends DBSCAN for clustering by creating an ordering of data points based 
+on their reachability distance. It is designed to identify clusters in spatial datasets using 
+density-based methods.
+Parameters
+----------
+    The number of samples in a neighborhood required to consider a point as a core point.
+    If float, should be between 0 and 1 and will be interpreted as a fraction of the total number of samples.
+    Maximum reachability distance within which to search for clusters. Determines the maximum 
+    radius of a cluster. Higher values may return more clusters that are smaller and closer together.
+    The metric used to compute distances between instances in a feature array. Options include 
+    'cityblock', 'cosine', 'euclidean', etc., or a custom function. 
+    Power parameter for the Minkowski metric. When p=1 it is equivalent to using manhattan_distance (l1),
+    and when p=2 it is equivalent to using euclidean_distance (l2).
+    Additional keyword arguments for the metric function.
+    Determines whether to use X-means clustering ('xi') or DBSCAN as the method of constructing clusters 
+    The maximum distance between two samples for one to be considered as in the neighborhood of the other 
+    Parameter used in X-means clustering that measures density.
+    Determines whether predecessor correction is applied in X-Means to handle noise.
+    The minimum number of samples for a cluster. If float, should be between 0 and 1 
+    and will be interpreted as a fraction of the total number of samples.
+    Algorithm used to compute the OPTICS graph. 'auto' tries BallTree first; otherwise,
+    falls back on brute force approach.
+    Leaf size passed as a parameter to the BallTree or KDTree. Controls when the tree 
+    building algorithm switches from brute force.
+    If specified, use joblib.Memory caching with this directory.
+    The number of parallel jobs to run for neighbors search. If n_jobs=-1, all CPUs are used.
+Returns
+-------
+    Returns the fitted model itself, allowing method chaining.
+Attributes
+----------
+    Cluster labels for each point in the dataset.
+    Ordering of points by reachability distance.
+    Core distances of points.
+    Reachability distances between samples.
+    Predecessors of each point in the ordering list.
+    Hierarchy of clusters (only when cluster_method='xi').
+Raises
+------
+ValueError
+    If 'dbscan' is selected as cluster_method and eps is not provided, or if 
+    eps &gt; max_eps.
+DataConversionWarning
+    If the metric requires boolean data but input data is not boolean, a warning 
+    will be issued to convert data before fitting.
+Notes
+-----
+This class extends Scikit-Learn's BaseEstimator and ClusterMixin. It allows for 
+method chaining with its fit method returning self.
+Examples
+--------
+&gt;&gt;&gt; from sklearn.cluster import OPTICS
+&gt;&gt;&gt; model = OPTICS(min_samples=5, max_eps=0.5)
+&gt;&gt;&gt; model.fit(X)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -16116,7 +16856,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>OrdinalEncoder is a class designed to encode categorical features as ordinal values,
+which can be useful for machine learning algorithms that require numerical input.
+Parameters:
+  Options are 'error' (raises an error) or 'use_encoded_value' (assigns a unique value). 
+Methods:
+  Returns self.
+Returns:
+The `fit` method returns self after fitting the encoder with training data. The `transform` 
+and `inverse_transform` methods return encoded or decoded arrays/DataFrames respectively.
+Functionality:
+This class supports encoding categorical features as ordinal values, handling missing and unknown values,
+based on specified parameters. It includes functionality to manage infrequent categories by a maximum
+limit of unique values per feature.
+Exceptions:
+Raises TypeError if 'unknown_value' is set incorrectly when handle_unknown='use_encoded_value'.
+Raises ValueError for invalid unknown_value settings or mismatched data shapes during transformation.
+Ensures appropriate handling of missing and unknown category cases, raising exceptions as needed.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -16288,7 +17044,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Pooling1D Layer
+This class defines a custom 1-dimensional pooling layer in TensorFlow's Keras API, 
+extending from the base `Layer` class. It is used within deep learning models to perform 
+downsampling operations on input tensors, aiding in feature extraction.
+Parameters:
+                              such as MaxPooling1D or AveragePooling1D.
+                                     or a tuple specifying dimensions; defaults to 2 if not provided.
+                             Default is 'valid'.
+                                 (default) or 'channels_first', indicating where channels are positioned.
+Returns:
+    Layer instance that can be added to a Keras model to apply 1D pooling on input tensors.
+Functionality:
+- Initializes with specified parameters for pooling operation.
+- Applies pooling transformation in the `call` method using provided `pool_function`.
+- Computes output shape of the layer given an input shape in `compute_output_shape`.
+- Provides configuration details via `get_config` for model serialization.
+Exceptions:
+- Input validation is not performed within this class, which may raise errors if parameters
+  are incorrect or incompatible.
+- Assumes correct handling by `pool_function` based on data format ('channels_last'/'channels_first').
+- May produce unexpected results if non-positive strides or pool sizes are used.
+This layer can be utilized in convolutional neural networks for preprocessing and feature 
+extraction, with customizable pooling functions, padding options, and data formats.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -16479,7 +17257,20 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Pooling2D Layer
+This class defines a custom Pooling2D layer in Keras, which applies pooling operations to reduce the spatial size of input tensors.
+Parameters:
+Returns:
+- The method call returns a tensor representing the pooled output, which can be a Numpy array or TensorFlow/Theano tensor depending on the backend used.
+Functionality:
+This code defines a Pooling2D layer that applies a pooling operation (specified by `pool_function`) to an input layer in two dimensions. It uses the `call` method to apply this operation with parameters like pool size, strides, padding style, and data format.
+Exceptions:
+- Type errors may be raised if `pool_size`, `strides`, or `padding` are not correctly specified.
+- Value errors occur if `data_format` is neither 'channels_first' nor 'channels_last'.
+- Input shape compatibility must ensure the input tensor has exactly 4 dimensions (batch size, height, width, channels).
+Additional Methods:
+Note:
+Ensure that inputs to the layer are correctly shaped and that all parameters adhere to expected types and values to avoid runtime exceptions.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -16683,7 +17474,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Pooling3D Layer for Keras
+The `Pooling3D` class is a custom layer in Keras designed to perform 3-dimensional pooling operations 
+on input tensors. This layer is commonly used after convolutional layers to reduce the spatial size of 
+the inputs, thereby decreasing computational costs and mitigating overfitting.
+Parameters:
+Returns:
+The `call` method returns an output tensor with reduced dimensions, maintaining rank equivalent 
+to input but condensed along spatial axes. The `compute_output_shape` method predicts the shape of this output given an input shape.
+Functionality:
+This layer applies a specified pooling operation over 3D windows defined by `pool_size`, sliding across each dimension
+as dictated by `strides`. This process is crucial for reducing feature map sizes in deep learning models, 
+facilitating downsampling without losing critical information. The class supports configuration saving via `get_config` method.
+Exceptions:
+This layer assumes inputs are rank-5 tensors with either 'channels_last' or 'specified' data formats.
+Invalid parameter values such as non-positive pool sizes or incorrect data types for pooling functions may trigger exceptions, 
+typically resulting in a ValueError. While the code does not explicitly handle input shape mismatches (e.g., fewer than three dimensions),
+such discrepancies can lead to unexpected errors during execution.
+Overall, `Pooling3D` serves as an integral component for structuring and optimizing deep learning models that process volumetric data.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -17013,7 +17821,64 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>PrincipalComponentAnalysis Class
+This class implements a Principal Component Analysis (PCA) model using Singular Value Decomposition 
+(SVD) or Eigen decomposition methods for dimensionality reduction and exploratory data analysis.
+Parameters:
+                                   Default is None.
+                            Decomposition or 'svd' for Singular Value Decomposition. Default is 'svd'.
+                                principal component axis. Default is False.
+Methods:
+    __init__(self, n_components=None, solver='svd', whitening=False):
+        Initializes an instance of PrincipalComponentAnalysis with the specified parameters.
+        Returns:
+            self (PrincipalComponentAnalysis)
+    fit(self, X, y=None):
+        Fits the model using input data X. Raises errors if `n_components` is not a positive integer 
+        or None, and checks for valid solver.
+        Parameters:
+                Input data.
+        Returns:
+            self (PrincipalComponentAnalysis), bool
+                Fitted instance and fit state as boolean.
+    transform(self, X):
+        Projects input data X into the new feature space using the learned transformation matrix. 
+        Applies optional whitening if specified during initialization.
+        Parameters:
+                Input data to be transformed.
+        Returns:
+            numpy.ndarray
+                Transformed data as a numpy array.
+    _covariance_matrix(self, X):
+        Calculates and returns the covariance matrix of input X used for PCA decomposition.
+        Parameters:
+                Input data.
+        Returns:
+            numpy.ndarray
+                Covariance matrix as a 2D numpy array.
+    _decomposition(self, mat, n_samples):
+        Performs Eigen decomposition or Singular Value Decomposition to obtain eigenvalues and 
+        eigenvectors from the input matrix.
+        Parameters:
+                Input matrix for decomposition.
+        Returns:
+            tuple
+                Eigenvalues as a 1D numpy array and eigenvectors as a 2D numpy array.
+    _loadings(self):
+        Calculates and returns the loadings matrix, which combines eigenvectors and eigenvalues 
+        Returns:
+            numpy.ndarray
+                Loadings as a 2D numpy array.
+    _projection_matrix(self, eig_vals, eig_vecs, whitening, n_components):
+        Constructs and returns the projection matrix used for transforming input data using learned parameters.
+        Parameters:
+                Eigenvalues from decomposition.
+                Eigenvectors from decomposition.
+        Returns:
+            numpy.ndarray
+                Projection matrix as a 2D numpy array.
+Exceptions:
+                    and not None. Also raised if attempting to transform data without fitting the model first.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -17439,7 +18304,18 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>RMSProp Optimizer Implementation
+This class implements the RMSProp optimization algorithm using TensorFlow, extending from `optimizer_v2.OptimizerV2`. RMSProp is an adaptive learning rate method designed to adjust the learning rate based on a moving average of squared gradients.
+Parameters:
+Returns:
+    None explicitly; updates model weights in place through gradient descent with adaptive learning rates.
+Functionality:
+The optimizer computes a moving average of the squared gradients for each weight and adjusts the step size accordingly. It supports both dense and sparse gradient applications, utilizing methods `_resource_apply_dense` and `_resource_apply_sparse`.
+Exceptions:
+Raises ValueError if `momentum` is not within [0, 1]. Other potential exceptions include TensorFlow operation errors (e.g., invalid slots) and runtime errors like division by zero.
+Other Features:
+Edge Cases:
+Handles scenarios such as zero learning rate, zero gradients, and large update values to prevent numerical instability.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -18178,7 +19054,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class implements a self-training approach to enhance model performance using both labeled and unlabeled data. It iteratively refines its predictions on unlabeled instances until convergence or a specified maximum number of iterations is reached.
+Parameters:
+Returns:
+Raises:
+Methods:
+The self-training loop iteratively uses predictions from the current model to label unlabeled instances with high confidence, refining the model until all instances are labeled or maximum iterations are reached.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -18437,7 +19318,31 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Class `SeparableConv` implements a separable convolution layer by extending 
+the `Conv` class from TensorFlow's Keras API, utilizing depthwise and pointwise 
+convolutions for efficiency.
+Parameters:
+  For uniform size, a single integer can be provided.
+  "channels_first"). Inherited via `super(SeparableConv, self).__init__`.
+  Defaults to 1.
+  'glorot_uniform', 'glorot_uniform', and 'zeros' respectively.
+Returns:
+A dictionary containing configuration parameters such as filters, kernel_size, strides, padding, data_format,
+depth_multiplier, dilation_rate, activation, use_bias, and initializers/regularizers/constraints for serialization 
+and deserialization purposes via `get_config()` method.
+Exceptions:
+Raises ValueError if the channel dimension of inputs is undefined. Other potential exceptions include incorrect 
+data input shape or improper initialization parameters leading to weight value errors.
+Functionality:
+This class initializes with specified arguments and builds layer weights (`depthwise_kernel`, `pointwise_kernel`, 
+and optionally a bias vector) in the `build()` method based on input shapes. The `call()` method is intended for
+applying separable convolution operations but raises NotImplementedError, requiring implementation by subclasses.
+Attributes:
+- Various initializers, regularizers, and constraints for depthwise and pointwise kernels.
+Examples of usage should ensure correct parameter specification, especially regarding the rank, filters,
+and kernel_size dimensions to avoid exceptions related to incorrect data input shapes or weight initialization errors.
+This class is designed with extensibility in mind, allowing custom implementations of convolutional operations 
+via subclassing and overriding the `call()` method.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -18715,7 +19620,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class `SeparableConv1D` implements a separable convolution operation for 1-dimensional input data, 
+inheriting from a parent class `SeparableConv`. It is designed to handle sequential data such as time series or audio samples.
+Parameters:
+Other parameters include initializers, regularizers, and constraints for weights, which can be strings or objects.
+Functionality:
+The `call` method performs the separable 1D convolution on inputs. If padding is 'causal', it pads inputs with zeros.
+It adjusts strides based on data format, computes output shape, and executes depthwise and pointwise convolutions using TensorFlow's `nn` module. Bias can be added if specified, and outputs may pass through an activation function.
+Returns:
+- The `call` method returns a tensor representing the separable 1D convolution output.
+Exceptions/Edge Cases:
+- No specific exceptions are raised by this snippet if valid parameters are provided.
+- Errors occur at points where invalid arguments are used in method calls.
+- Edge cases may arise from mismatched input dimensions or incorrect spatial dimensions for kernel size, filters, etc.
+Note:
+This implementation assumes correct definitions of TensorFlow functions like `nn.separable_conv2d` and appropriate input dimensions. 
+Memory usage considerations apply based on system configuration.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -18972,7 +19892,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Class SeparableConv2D
+This class extends TensorFlow's Keras `SeparableConv` to implement a 2-dimensional separable convolution layer, 
+known for its efficiency in reducing parameters and computations compared to standard convolutions.
+Attributes:
+                   Defaults to 'valid'.
+                                 Default is None.
+Other Parameters:
+      or constrain their values during optimization.
+Methods:
+                separable convolution functionality by calling `super().__init__()`.
+                  applicable, and applies an activation function.
+Exceptions:
+    - Raises a `ValueError` at runtime if inputs do not have the correct dimensions or data format.
+    - Raises a `KeyError` if an unsupported activation function is specified.
+Functionality:
+The class uses depthwise and pointwise convolutions for efficient computation, reducing the number of parameters 
+and potentially speeding up training. It supports flexible input configurations with various initializers, regularizers,
+and constraints to tailor model architecture as needed.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -20254,7 +21191,28 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Class SequentialFeatureSelector
+The `SequentialFeatureSelector` class implements sequential feature selection for 
+machine learning models using cross-validation to evaluate subsets of features. It is designed 
+to optimize model performance by selecting the most relevant subset of input features, which can help 
+prevent overfitting in situations with a large number of features.
+Parameters:
+  Any object that satisfies this criterion is valid, though not all may support features like
+  feature names.
+  a tuple specifying minimum and maximum numbers of features, or 'best'/'parsimonious'.
+  and removed in each iteration to optimize performance further.
+  the type of estimator (e.g., 'accuracy' for classifiers).
+  in selected subsets.
+Returns:
+The class provides several methods for transforming data based on selected features and retrieving
+performance metrics. Key methods include:
+  confidence intervals and standard deviations.
+Exceptions:
+Raises various exceptions to handle incorrect parameter inputs or method usage:
+Functionality:
+The class facilitates sequential feature selection through either forward or backward elimination,
+optimized by cross-validation scores. It includes mechanisms to evaluate and adjust selected 
+feature subsets iteratively, allowing both fixed and floating selections based on performance.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -20531,7 +21489,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Stochastic Gradient Descent (SGD) Optimizer
+This class implements the Stochastic Gradient Descent optimizer, inheriting from TensorFlow's `optimizer_v2.OptimizerV2`. It is used for optimizing neural network parameters through gradient descent methods. Key features include configurable learning rate, momentum, and Nesterov Momentum.
+Parameters:
+Returns:
+    This class does not explicitly return values from its methods but alters variable states during optimization. The `get_config()` method returns a dictionary with current configuration settings.
+Functionality:
+    Implements the SGD optimization algorithm, using gradient information to iteratively update model weights based on training examples. Supports momentum and Nesterov Momentum for accelerated learning convergence.
+Exceptions:
+    Raises ValueError if 'momentum' is not between 0 and 1 or if invalid types are used. Potential issues include negative learning rates or improper initialization of optimizer state slots.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -20855,7 +21821,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Softmax Regression Model Class
+This class implements a Softmax Regression model for multi-class classification using numpy for computations.
+Parameters:
+Attributes:
+Methods:
+Returns:
+The constructor does not return anything. The `_fit` and `predict_proba` methods return the instance itself for method chaining.
+Exceptions:
+Ensure that inputs satisfy method requirements, such as matching shapes and valid parameter values. Potential exceptions include TypeErrors or ValueErrors from mismatched input dimensions or invalid types.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -21568,7 +22542,26 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>TargetEncoder class implements target encoding, a technique for encoding categorical 
+variables by replacing them with the mean of the target variable in specific dataset splits.
+Parameters:
+  'Auto' infers the categories from data.
+  or 'auto' to infer it automatically (default='auto').
+  (default='auto' or a non-negative float).
+  (default=None).
+Methods:
+Returns:
+- Instance methods typically return self for method chaining or transformed arrays. The
+  fit and transform processes utilize internal state changes within the instance to apply 
+  encodings based on target means per category.
+Exceptions:
+- Raises TypeError if parameter types do not meet constraints.
+- Raises ValueError if unsupported target type is inferred, input data contains NaNs, or 
+  smooth value is negative.
+- Check_is_fitted errors are raised for attempts to transform data without prior fitting.
+Overall, the TargetEncoder class facilitates encoding of categorical features with respect
+to a target variable, aiding in reducing overfitting and improving model performance through 
+target mean-based transformations.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -21843,7 +22836,13 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>TransactionEncoder is a transformer class that converts lists of items (transactions) into one-hot encoded arrays suitable for use with machine learning algorithms. It inherits from scikit-learn's `BaseEstimator` and `TransformerMixin`.
+Methods:
+3. transform(self, X, sparse=False): Converts a list of transactions into a binary matrix representation. Parameters are:
+   Returns a 2D numpy array or a sparse matrix with rows representing transactions and columns representing items, where the value at position (i, j) is True if item j is present in transaction i.
+Attributes:
+Raises:
+The class ensures methods that require prior fitting are not called prematurely by checking fitted attributes. It supports both dense and sparse outputs for memory efficiency in large datasets.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -21976,7 +22975,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>The UpSampling1D class is a Keras Layer used for upsampling one-dimensional data, typically in time-series or sequences. It extends the base `Layer` class and allows its integration into neural network models to increase the resolution of input tensors along their second dimension (the temporal/sequence axis).
+Parameters:
+Returns:
+    The `compute_output_shape` method returns a TensorShape object representing the output shape if the input tensor were passed through this layer, taking into account the specified input shape. It doubles (or multiplies by `size`) the second dimension.
+    The `call` method performs the actual upsampling operation on its input, returning the repeated elements along the sequence axis.
+Functionality:
+    This layer increases the length of a 3D input tensor along its second dimension by repeating each element according to the specified `size`. It is crucial for handling variations in temporal resolution or frame rates. The class includes key methods such as `__init__` for initialization, `compute_output_shape` for output shape calculation, and `call` for performing upsampling.
+    Additionally, `get_config` returns a configuration dictionary that can be used to recreate the layer during model serialization/deserialization.
+Exceptions:
+    While this code does not explicitly raise exceptions, it relies on Keras/TensorFlow to handle errors. Potential issues include input shape mismatches or backend compatibility problems leading to ValueErrors or NotImplementedError. The layer requires inputs with exactly three dimensions and expects `size` to be an integer.
+The class is defined as follows:
+        super(UpSampling1D, self).__init__(**kwargs)
+        input_shape = tensor_shape.TensorShape(input_shape).as_list()
+        size = self.size * input_shape[1] if input_shape[1] is not None else None
+        output = backend.repeat_elements(inputs, self.size, axis=1)
+        base_config = super(UpSampling1D, self).get_config()</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -22178,7 +23192,26 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Custom Keras Layer for Upsampling 2D Input Tensors
+This class, `UpSampling2D`, is a custom layer designed to resize the spatial dimensions (height and width) of 2D input tensors by a specified factor. It extends the base `Layer` class provided by Keras and can be used in neural network models for tasks that require upsampling.
+Parameters
+----------
+    Tuple representing the factors by which the height and width should be resized. Default is (2, 2).
+    String representing the data format of the input tensors. If not provided, Keras uses the default from the configuration file.
+    String specifying the interpolation method used for resizing. Default is 'nearest'.
+**kwargs :
+    Additional keyword arguments to pass to the base `Layer` class.
+Returns
+-------
+tensor
+    A tensor with upscaled spatial dimensions, maintaining the same number of channels as the input tensor. The output shape depends on the `size` parameter and `data_format`.
+Functionality
+-------------
+The `UpSampling2D` layer performs upsampling by increasing the height and width of its inputs using either nearest neighbor or bilinear interpolation methods specified at initialization. It is particularly useful in deep learning tasks like semantic segmentation, where maintaining spatial resolution is crucial.
+Exceptions
+----------
+- Raises a `ValueError` if an invalid `interpolation` method is provided (must be one of 'nearest' or 'bilinear').
+- The layer expects input tensors with four dimensions; any deviation will result in runtime errors when using the TensorFlow backend.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -22349,7 +23382,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>`UpSampling3D` is a Keras layer that performs upsampling of 3-dimensional data, typically used in contexts involving recurrent neural networks or 3D convolutions. It increases spatial dimensions by repeating elements, particularly useful for operations like semantic segmentation and style transfer.
+Parameters:
+- `data_format`: A string, one of 'channels_first' or 'channels_last' (default=None). Specifies the format of input and output tensors:
+Returns:
+This class does not return values directly but manipulates data through methods like `call`, which performs the upsampling operation using Keras backend functions, and `compute_output_shape`, which calculates the expected output shape.
+Functionality:
+Exceptions:
+The class may raise exceptions under certain conditions:
+- `ValueError` for unsupported data formats or invalid input shapes.
+- TensorFlow backend functions like `resize_volumes` might raise errors if inputs are not as expected, such as incorrect data types or incompatible dimensions.
+Usage typically involves integrating this layer into larger models where spatial dimensionality needs to be increased. It is crucial to ensure that input tensors meet the required 5D shape and format specifications.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -22503,7 +23546,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Custom Keras Layer for Zero Padding in Temporal Dimension
+This class `ZeroPadding1D` is a custom layer designed to apply zero padding to the temporal dimension of one-dimensional input tensors, such as sequences or word embeddings.
+Parameters:
+Returns:
+- The `compute_output_shape(input_shape)` method returns a TensorShape object representing the shape of the output tensor after padding, based on the input shape and applied transformations.
+- The `call(inputs)` method accepts tensors with shape `(batch_size, timesteps, features)`, applies zero-padding along the temporal dimension using Keras backend's `temporal_padding` function, and returns a padded tensor.
+- The `get_config()` method returns a dictionary containing configuration details needed to recreate this layer during model serialization.
+Functionality:
+This class provides functionality for temporal zero-padding, essential in preparing sequences for recurrent neural networks (RNNs). It adds zeros along the time dimension of each sequence without altering other dimensions. The padding is applied as specified by the `padding` parameter during initialization.
+Exceptions:
+Ensure that inputs to the `call()` method match expected specifications (3-dimensional tensors). Type errors may occur if non-integer values are provided for `padding`. The class does not inherently handle edge cases like empty inputs, so users must validate input data before use. Invalid padding values or unspecified input dimensions can lead to runtime exceptions.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -22777,7 +23830,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>This class implements a Zero Padding 2D layer for convolutional neural networks using Keras.
+Parameters:
+Returns:
+The `ZeroPadding2D` layer returns a tensor with zero-padded rows and/or columns. The output shape of this layer is calculated by the `compute_output_shape` method, which considers the input shape, padding values, and data format.
+Functionality:
+This layer adds zeros around the border of images without altering their content or size, preserving spatial information crucial for tasks like edge detection in convolutional neural networks. It supports both symmetric and asymmetric padding configurations.
+Exceptions:
+Raises ValueError if `padding` is not an integer or a tuple with correct dimensions (either two integers or two tuples each containing two integers). Also raises ValueError if `data_format` is neither 'channels_first' nor 'channels_last'.
+The `compute_output_shape` method calculates the output tensor shape by adding specified padding values to the input dimensions. The `call` method applies zero-padding using Keras's backend function, and `get_config` returns layer configuration for serialization.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -23054,7 +24115,35 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>Custom Keras Layer for Zero Padding in 3D Convolutional Neural Networks.
+This class, `ZeroPadding3D`, extends the base Keras Layer to perform zero padding on inputs,
+which is crucial for preventing information loss at feature map borders during convolution operations.
+It supports various configurations of padding and data formats, making it versatile for different
+use cases in 3D CNNs.
+Parameters:
+  a tuple of three integers, or a tuple of three tuples specifying symmetric padding for each dimension.
+  For example:
+      every dimension.
+      `padding=(2, 3, 4)` pads dimension 1 by 2, dimension 2 by 3 on both sides, and dimension 3 by 4.
+      `padding=((1,0),(1,2),(1,3))` adds 1 zero to the left side of dimension 1, no zeros to
+      dimension 2, and 3 zeros to the right side of dimension 3.
+  'channels_last'. If None, defaults to `keras.backend.image_data_format()`.
+Returns:
+A class definition for `ZeroPadding3D`, which provides methods for initialization,
+computing output shape, performing forward pass computations, and retrieving layer configuration.
+Methods:
+  specified padding and data format. Raises ValueError if `padding` is not properly formatted.
+  adjusting for applied padding.
+Exceptions:
+Raises ValueError if `padding` is not of length 3 or its elements are not integers. Also raises
+ValueError if any tuple in `padding` does not contain exactly two integers.
+Functionality:
+The layer adds zeros around an input tensor to expand spatial dimensions without altering the
+spatial structure, aiding in data augmentation and preventing size reduction during downsampling.
+It supports both 'channels_first' and 'channels_last' data formats for flexibility across frameworks.
+This implementation is essential for maintaining feature map sizes in 3D CNNs while ensuring that
+augmented inputs retain their spatial properties, crucial for models sensitive to image dimensions
+or aspect ratios.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -23713,7 +24802,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t># ERROR: GoT Generation failed</t>
+          <t>_BaseEncoder provides a base set of functionalities for encoding categorical variables and can be used as 
+a building block for more complex encoding models. It supports various methods to fit, transform, and handle 
+categorical data, including managing infrequent categories.
+Parameters:
+  - Options are 'error' (raise an error) or 'ignore' (fill with default).
+- return_counts, return_and_ignore_missing_for_infrequent: 
+  which categories to ignore in case of infrequent categorization.
+Attributes:
+  and mapping strategies.
+Methods:
+  optionally returning counts.
+Exceptions:
+- Raises ValueError for incompatible categories or missing elements in user-defined categories.
+- Raises UserWarning for unknown categories when `warn_on_unknown` is True.
+This class provides robust error checking to ensure correct usage of methods and maintains data integrity. 
+It handles various scenarios related to categorical data preprocessing, including managing infrequent categories
+and ensuring compatibility with numerical operations.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
